--- a/Fase 2/Evidencias Proyecto/Sprint Backlogs/SIGMA_Sprint_Backlog_S3.xlsx
+++ b/Fase 2/Evidencias Proyecto/Sprint Backlogs/SIGMA_Sprint_Backlog_S3.xlsx
@@ -25211,7 +25211,7 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -25231,7 +25231,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -25251,7 +25251,7 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -25271,7 +25271,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -25291,7 +25291,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -25331,7 +25331,7 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -25351,7 +25351,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -25371,10 +25371,11 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="19">
       <c r="A16" s="20" t="inlineStr">
         <is>
